--- a/Team-Data/2012-13/1-18-2012-13.xlsx
+++ b/Team-Data/2012-13/1-18-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2" t="n">
         <v>22</v>
       </c>
       <c r="F2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.579</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
@@ -688,28 +755,28 @@
         <v>8.699999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0.375</v>
+        <v>0.374</v>
       </c>
       <c r="O2" t="n">
         <v>13.2</v>
       </c>
       <c r="P2" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="Q2" t="n">
         <v>0.703</v>
       </c>
       <c r="R2" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="S2" t="n">
         <v>30.7</v>
       </c>
       <c r="T2" t="n">
-        <v>40.4</v>
+        <v>40.6</v>
       </c>
       <c r="U2" t="n">
         <v>23.2</v>
@@ -721,31 +788,31 @@
         <v>8.4</v>
       </c>
       <c r="X2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.9</v>
+        <v>17.7</v>
       </c>
       <c r="AA2" t="n">
         <v>18.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>95.59999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AE2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -754,7 +821,7 @@
         <v>11</v>
       </c>
       <c r="AI2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ2" t="n">
         <v>22</v>
@@ -787,19 +854,19 @@
         <v>16</v>
       </c>
       <c r="AT2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV2" t="n">
         <v>16</v>
       </c>
       <c r="AW2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -843,58 +910,58 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3" t="n">
         <v>20</v>
       </c>
       <c r="F3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G3" t="n">
-        <v>0.513</v>
+        <v>0.526</v>
       </c>
       <c r="H3" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="I3" t="n">
         <v>36.9</v>
       </c>
       <c r="J3" t="n">
-        <v>79.8</v>
+        <v>79.5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.463</v>
+        <v>0.464</v>
       </c>
       <c r="L3" t="n">
         <v>5.5</v>
       </c>
       <c r="M3" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0.339</v>
+        <v>0.341</v>
       </c>
       <c r="O3" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="P3" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.775</v>
+        <v>0.777</v>
       </c>
       <c r="R3" t="n">
         <v>8.4</v>
       </c>
       <c r="S3" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T3" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
       <c r="U3" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="V3" t="n">
         <v>14.3</v>
@@ -906,40 +973,40 @@
         <v>4.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="AA3" t="n">
         <v>19.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.2</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="AC3" t="n">
         <v>-0.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AE3" t="n">
         <v>15</v>
       </c>
       <c r="AF3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI3" t="n">
         <v>15</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK3" t="n">
         <v>6</v>
@@ -951,10 +1018,10 @@
         <v>28</v>
       </c>
       <c r="AN3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP3" t="n">
         <v>24</v>
@@ -972,25 +1039,25 @@
         <v>30</v>
       </c>
       <c r="AU3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AV3" t="n">
         <v>8</v>
       </c>
       <c r="AW3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX3" t="n">
         <v>26</v>
       </c>
       <c r="AY3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BA3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB3" t="n">
         <v>19</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -1025,88 +1092,88 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F4" t="n">
         <v>16</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="J4" t="n">
-        <v>79.7</v>
+        <v>79.8</v>
       </c>
       <c r="K4" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L4" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M4" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0.343</v>
+        <v>0.342</v>
       </c>
       <c r="O4" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="P4" t="n">
-        <v>24.8</v>
+        <v>24.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.752</v>
+        <v>0.755</v>
       </c>
       <c r="R4" t="n">
         <v>12.7</v>
       </c>
       <c r="S4" t="n">
-        <v>29.4</v>
+        <v>29.2</v>
       </c>
       <c r="T4" t="n">
-        <v>42</v>
+        <v>41.8</v>
       </c>
       <c r="U4" t="n">
         <v>20.2</v>
       </c>
       <c r="V4" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="W4" t="n">
         <v>7.3</v>
       </c>
       <c r="X4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.59999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF4" t="n">
         <v>9</v>
@@ -1115,16 +1182,16 @@
         <v>10</v>
       </c>
       <c r="AH4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI4" t="n">
         <v>26</v>
       </c>
       <c r="AJ4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
         <v>12</v>
@@ -1133,22 +1200,22 @@
         <v>9</v>
       </c>
       <c r="AN4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO4" t="n">
         <v>7</v>
       </c>
       <c r="AP4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR4" t="n">
         <v>7</v>
       </c>
       <c r="AS4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AT4" t="n">
         <v>16</v>
@@ -1157,13 +1224,13 @@
         <v>25</v>
       </c>
       <c r="AV4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW4" t="n">
         <v>25</v>
       </c>
       <c r="AX4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY4" t="n">
         <v>6</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -1207,43 +1274,43 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="n">
         <v>29</v>
       </c>
       <c r="G5" t="n">
-        <v>0.256</v>
+        <v>0.237</v>
       </c>
       <c r="H5" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I5" t="n">
         <v>34.9</v>
       </c>
       <c r="J5" t="n">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.424</v>
+        <v>0.423</v>
       </c>
       <c r="L5" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="M5" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="O5" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="P5" t="n">
-        <v>26.1</v>
+        <v>25.8</v>
       </c>
       <c r="Q5" t="n">
         <v>0.746</v>
@@ -1252,16 +1319,16 @@
         <v>11.8</v>
       </c>
       <c r="S5" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T5" t="n">
         <v>41.3</v>
       </c>
       <c r="U5" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="V5" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W5" t="n">
         <v>7.4</v>
@@ -1270,31 +1337,31 @@
         <v>6.3</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AB5" t="n">
-        <v>95.09999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AE5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AF5" t="n">
         <v>28</v>
       </c>
       <c r="AG5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH5" t="n">
         <v>6</v>
@@ -1315,7 +1382,7 @@
         <v>27</v>
       </c>
       <c r="AN5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO5" t="n">
         <v>3</v>
@@ -1339,7 +1406,7 @@
         <v>30</v>
       </c>
       <c r="AV5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW5" t="n">
         <v>22</v>
@@ -1357,7 +1424,7 @@
         <v>4</v>
       </c>
       <c r="BB5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BC5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1456,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F6" t="n">
         <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>0.605</v>
+        <v>0.595</v>
       </c>
       <c r="H6" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I6" t="n">
         <v>35.5</v>
       </c>
       <c r="J6" t="n">
-        <v>80.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="K6" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L6" t="n">
         <v>4.6</v>
@@ -1422,73 +1489,73 @@
         <v>0.358</v>
       </c>
       <c r="O6" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P6" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.784</v>
+        <v>0.786</v>
       </c>
       <c r="R6" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S6" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="T6" t="n">
         <v>43.7</v>
       </c>
       <c r="U6" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="V6" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="W6" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y6" t="n">
         <v>5.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>94.09999999999999</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC6" t="n">
         <v>2.2</v>
       </c>
       <c r="AD6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH6" t="n">
         <v>23</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>14</v>
       </c>
       <c r="AI6" t="n">
         <v>24</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL6" t="n">
         <v>30</v>
@@ -1497,7 +1564,7 @@
         <v>30</v>
       </c>
       <c r="AN6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO6" t="n">
         <v>8</v>
@@ -1509,7 +1576,7 @@
         <v>6</v>
       </c>
       <c r="AR6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS6" t="n">
         <v>12</v>
@@ -1518,31 +1585,31 @@
         <v>7</v>
       </c>
       <c r="AU6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW6" t="n">
         <v>23</v>
       </c>
       <c r="AX6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AY6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BB6" t="n">
         <v>25</v>
       </c>
       <c r="BC6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-5.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
         <v>28</v>
@@ -1658,7 +1725,7 @@
         <v>30</v>
       </c>
       <c r="AG7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AH7" t="n">
         <v>26</v>
@@ -1685,10 +1752,10 @@
         <v>18</v>
       </c>
       <c r="AP7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR7" t="n">
         <v>4</v>
@@ -1697,13 +1764,13 @@
         <v>30</v>
       </c>
       <c r="AT7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU7" t="n">
         <v>29</v>
       </c>
       <c r="AV7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW7" t="n">
         <v>9</v>
@@ -1721,7 +1788,7 @@
         <v>12</v>
       </c>
       <c r="BB7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BC7" t="n">
         <v>27</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -1753,25 +1820,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E8" t="n">
         <v>17</v>
       </c>
       <c r="F8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G8" t="n">
-        <v>0.415</v>
+        <v>0.425</v>
       </c>
       <c r="H8" t="n">
-        <v>49.2</v>
+        <v>49.1</v>
       </c>
       <c r="I8" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J8" t="n">
-        <v>83.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="K8" t="n">
         <v>0.449</v>
@@ -1786,61 +1853,61 @@
         <v>0.356</v>
       </c>
       <c r="O8" t="n">
-        <v>17.6</v>
+        <v>17.4</v>
       </c>
       <c r="P8" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.793</v>
+        <v>0.792</v>
       </c>
       <c r="R8" t="n">
         <v>9.4</v>
       </c>
       <c r="S8" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="T8" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="U8" t="n">
         <v>22.1</v>
       </c>
       <c r="V8" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W8" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X8" t="n">
         <v>5.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z8" t="n">
         <v>21.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>99.90000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="AC8" t="n">
         <v>-3</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
         <v>18</v>
       </c>
       <c r="AF8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH8" t="n">
         <v>1</v>
@@ -1861,13 +1928,13 @@
         <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AP8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AQ8" t="n">
         <v>5</v>
@@ -1876,10 +1943,10 @@
         <v>27</v>
       </c>
       <c r="AS8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU8" t="n">
         <v>14</v>
@@ -1888,19 +1955,19 @@
         <v>13</v>
       </c>
       <c r="AW8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ8" t="n">
         <v>26</v>
       </c>
       <c r="BA8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E9" t="n">
         <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G9" t="n">
-        <v>0.571</v>
+        <v>0.585</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
@@ -1956,67 +2023,67 @@
         <v>85</v>
       </c>
       <c r="K9" t="n">
-        <v>0.465</v>
+        <v>0.464</v>
       </c>
       <c r="L9" t="n">
         <v>6.1</v>
       </c>
       <c r="M9" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0.328</v>
+        <v>0.326</v>
       </c>
       <c r="O9" t="n">
         <v>17.5</v>
       </c>
       <c r="P9" t="n">
-        <v>25.8</v>
+        <v>25.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.681</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="S9" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
       </c>
       <c r="T9" t="n">
-        <v>45.6</v>
+        <v>45.9</v>
       </c>
       <c r="U9" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="V9" t="n">
         <v>15.2</v>
       </c>
       <c r="W9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X9" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AA9" t="n">
         <v>21.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>102.7</v>
+        <v>102.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AD9" t="n">
         <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AF9" t="n">
         <v>12</v>
@@ -2025,7 +2092,7 @@
         <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI9" t="n">
         <v>2</v>
@@ -2067,10 +2134,10 @@
         <v>3</v>
       </c>
       <c r="AV9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX9" t="n">
         <v>4</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -2195,19 +2262,19 @@
         <v>-1.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
       </c>
       <c r="AF10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI10" t="n">
         <v>21</v>
@@ -2228,7 +2295,7 @@
         <v>7</v>
       </c>
       <c r="AO10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP10" t="n">
         <v>10</v>
@@ -2249,7 +2316,7 @@
         <v>24</v>
       </c>
       <c r="AV10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW10" t="n">
         <v>29</v>
@@ -2258,16 +2325,16 @@
         <v>9</v>
       </c>
       <c r="AY10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ10" t="n">
         <v>18</v>
       </c>
       <c r="BA10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC10" t="n">
         <v>18</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E11" t="n">
         <v>23</v>
       </c>
       <c r="F11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G11" t="n">
-        <v>0.605</v>
+        <v>0.622</v>
       </c>
       <c r="H11" t="n">
         <v>48.5</v>
@@ -2323,70 +2390,70 @@
         <v>0.456</v>
       </c>
       <c r="L11" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M11" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="N11" t="n">
-        <v>0.387</v>
+        <v>0.39</v>
       </c>
       <c r="O11" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="P11" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.793</v>
+        <v>0.792</v>
       </c>
       <c r="R11" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="S11" t="n">
         <v>34.3</v>
       </c>
       <c r="T11" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="U11" t="n">
         <v>22.9</v>
       </c>
       <c r="V11" t="n">
-        <v>15.4</v>
+        <v>15.6</v>
       </c>
       <c r="W11" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X11" t="n">
         <v>4</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z11" t="n">
         <v>21.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>100.1</v>
+        <v>100.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF11" t="n">
         <v>7</v>
       </c>
       <c r="AG11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH11" t="n">
         <v>10</v>
@@ -2398,7 +2465,7 @@
         <v>12</v>
       </c>
       <c r="AK11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AL11" t="n">
         <v>8</v>
@@ -2407,10 +2474,10 @@
         <v>12</v>
       </c>
       <c r="AN11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AO11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP11" t="n">
         <v>22</v>
@@ -2428,16 +2495,16 @@
         <v>3</v>
       </c>
       <c r="AU11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW11" t="n">
         <v>26</v>
       </c>
       <c r="AX11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY11" t="n">
         <v>16</v>
@@ -2446,7 +2513,7 @@
         <v>27</v>
       </c>
       <c r="BA11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB11" t="n">
         <v>9</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -2481,55 +2548,55 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E12" t="n">
         <v>21</v>
       </c>
       <c r="F12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G12" t="n">
-        <v>0.512</v>
+        <v>0.525</v>
       </c>
       <c r="H12" t="n">
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>38</v>
+        <v>38.2</v>
       </c>
       <c r="J12" t="n">
-        <v>83.2</v>
+        <v>83.3</v>
       </c>
       <c r="K12" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L12" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="M12" t="n">
         <v>28</v>
       </c>
       <c r="N12" t="n">
-        <v>0.357</v>
+        <v>0.355</v>
       </c>
       <c r="O12" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="P12" t="n">
-        <v>25.3</v>
+        <v>25.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.752</v>
+        <v>0.75</v>
       </c>
       <c r="R12" t="n">
         <v>10.6</v>
       </c>
       <c r="S12" t="n">
-        <v>32.3</v>
+        <v>32.5</v>
       </c>
       <c r="T12" t="n">
-        <v>42.8</v>
+        <v>43</v>
       </c>
       <c r="U12" t="n">
         <v>22.7</v>
@@ -2541,43 +2608,43 @@
         <v>8.699999999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA12" t="n">
         <v>19.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>105.1</v>
+        <v>105.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
         <v>13</v>
       </c>
       <c r="AF12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AG12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI12" t="n">
         <v>5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK12" t="n">
         <v>7</v>
@@ -2589,7 +2656,7 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AO12" t="n">
         <v>4</v>
@@ -2598,13 +2665,13 @@
         <v>6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AR12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AT12" t="n">
         <v>11</v>
@@ -2616,25 +2683,25 @@
         <v>30</v>
       </c>
       <c r="AW12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AY12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
         <v>10</v>
       </c>
       <c r="BA12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB12" t="n">
         <v>2</v>
       </c>
       <c r="BC12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -2663,97 +2730,97 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F13" t="n">
         <v>16</v>
       </c>
       <c r="G13" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>34.3</v>
+        <v>34.2</v>
       </c>
       <c r="J13" t="n">
-        <v>81.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="K13" t="n">
-        <v>0.422</v>
+        <v>0.42</v>
       </c>
       <c r="L13" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M13" t="n">
         <v>19.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0.339</v>
+        <v>0.333</v>
       </c>
       <c r="O13" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="P13" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.739</v>
+        <v>0.737</v>
       </c>
       <c r="R13" t="n">
         <v>13.1</v>
       </c>
       <c r="S13" t="n">
-        <v>33.2</v>
+        <v>33.4</v>
       </c>
       <c r="T13" t="n">
-        <v>46.3</v>
+        <v>46.4</v>
       </c>
       <c r="U13" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="V13" t="n">
         <v>14.9</v>
       </c>
       <c r="W13" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="X13" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z13" t="n">
         <v>19.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB13" t="n">
-        <v>91.5</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AD13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF13" t="n">
         <v>9</v>
       </c>
       <c r="AG13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH13" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI13" t="n">
         <v>30</v>
@@ -2765,19 +2832,19 @@
         <v>28</v>
       </c>
       <c r="AL13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM13" t="n">
         <v>16</v>
       </c>
       <c r="AN13" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ13" t="n">
         <v>23</v>
@@ -2786,7 +2853,7 @@
         <v>5</v>
       </c>
       <c r="AS13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT13" t="n">
         <v>1</v>
@@ -2795,7 +2862,7 @@
         <v>28</v>
       </c>
       <c r="AV13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW13" t="n">
         <v>27</v>
@@ -2804,10 +2871,10 @@
         <v>3</v>
       </c>
       <c r="AY13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA13" t="n">
         <v>7</v>
@@ -2816,7 +2883,7 @@
         <v>29</v>
       </c>
       <c r="BC13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -2923,10 +2990,10 @@
         <v>9</v>
       </c>
       <c r="AD14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
         <v>2</v>
@@ -2941,10 +3008,10 @@
         <v>3</v>
       </c>
       <c r="AJ14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
         <v>13</v>
@@ -2953,7 +3020,7 @@
         <v>11</v>
       </c>
       <c r="AN14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO14" t="n">
         <v>11</v>
@@ -2971,7 +3038,7 @@
         <v>17</v>
       </c>
       <c r="AT14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>1.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE15" t="n">
         <v>18</v>
@@ -3126,7 +3193,7 @@
         <v>19</v>
       </c>
       <c r="AK15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL15" t="n">
         <v>3</v>
@@ -3147,7 +3214,7 @@
         <v>29</v>
       </c>
       <c r="AR15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS15" t="n">
         <v>4</v>
@@ -3180,7 +3247,7 @@
         <v>4</v>
       </c>
       <c r="BC15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F16" t="n">
         <v>13</v>
       </c>
       <c r="G16" t="n">
-        <v>0.658</v>
+        <v>0.649</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
@@ -3227,85 +3294,85 @@
         <v>35.8</v>
       </c>
       <c r="J16" t="n">
-        <v>82.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="K16" t="n">
         <v>0.434</v>
       </c>
       <c r="L16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="M16" t="n">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0.343</v>
+        <v>0.342</v>
       </c>
       <c r="O16" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P16" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.796</v>
+        <v>0.799</v>
       </c>
       <c r="R16" t="n">
         <v>13.3</v>
       </c>
       <c r="S16" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T16" t="n">
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
       <c r="U16" t="n">
         <v>20.6</v>
       </c>
       <c r="V16" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W16" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y16" t="n">
         <v>5.8</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA16" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.40000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF16" t="n">
         <v>5</v>
       </c>
       <c r="AG16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI16" t="n">
         <v>22</v>
       </c>
       <c r="AJ16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK16" t="n">
         <v>24</v>
@@ -3317,10 +3384,10 @@
         <v>29</v>
       </c>
       <c r="AN16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP16" t="n">
         <v>18</v>
@@ -3335,25 +3402,25 @@
         <v>25</v>
       </c>
       <c r="AT16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU16" t="n">
         <v>23</v>
       </c>
       <c r="AV16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW16" t="n">
         <v>2</v>
       </c>
       <c r="AX16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AY16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA16" t="n">
         <v>13</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>5.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AE17" t="n">
         <v>4</v>
@@ -3499,13 +3566,13 @@
         <v>8</v>
       </c>
       <c r="AN17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP17" t="n">
         <v>13</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>12</v>
       </c>
       <c r="AQ17" t="n">
         <v>14</v>
@@ -3520,7 +3587,7 @@
         <v>29</v>
       </c>
       <c r="AU17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV17" t="n">
         <v>4</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -3651,19 +3718,19 @@
         <v>-1.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AE18" t="n">
         <v>15</v>
       </c>
       <c r="AF18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG18" t="n">
         <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI18" t="n">
         <v>12</v>
@@ -3681,16 +3748,16 @@
         <v>24</v>
       </c>
       <c r="AN18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP18" t="n">
         <v>20</v>
       </c>
       <c r="AQ18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR18" t="n">
         <v>6</v>
@@ -3699,10 +3766,10 @@
         <v>14</v>
       </c>
       <c r="AT18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV18" t="n">
         <v>9</v>
@@ -3720,7 +3787,7 @@
         <v>7</v>
       </c>
       <c r="BA18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB18" t="n">
         <v>16</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -3833,13 +3900,13 @@
         <v>-1.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG19" t="n">
         <v>18</v>
@@ -3851,7 +3918,7 @@
         <v>27</v>
       </c>
       <c r="AJ19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK19" t="n">
         <v>26</v>
@@ -3884,22 +3951,22 @@
         <v>5</v>
       </c>
       <c r="AU19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY19" t="n">
         <v>23</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA19" t="n">
         <v>2</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -4015,19 +4082,19 @@
         <v>-4</v>
       </c>
       <c r="AD20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE20" t="n">
         <v>26</v>
       </c>
       <c r="AF20" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG20" t="n">
         <v>26</v>
       </c>
       <c r="AH20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI20" t="n">
         <v>23</v>
@@ -4039,7 +4106,7 @@
         <v>15</v>
       </c>
       <c r="AL20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM20" t="n">
         <v>21</v>
@@ -4075,13 +4142,13 @@
         <v>28</v>
       </c>
       <c r="AX20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY20" t="n">
         <v>26</v>
       </c>
       <c r="AZ20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA20" t="n">
         <v>27</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>5</v>
       </c>
       <c r="AD21" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AE21" t="n">
         <v>5</v>
@@ -4215,7 +4282,7 @@
         <v>13</v>
       </c>
       <c r="AJ21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK21" t="n">
         <v>14</v>
@@ -4227,16 +4294,16 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO21" t="n">
         <v>22</v>
       </c>
       <c r="AP21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR21" t="n">
         <v>20</v>
@@ -4248,7 +4315,7 @@
         <v>26</v>
       </c>
       <c r="AU21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV21" t="n">
         <v>1</v>
@@ -4257,7 +4324,7 @@
         <v>7</v>
       </c>
       <c r="AX21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY21" t="n">
         <v>2</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -4301,28 +4368,28 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E22" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F22" t="n">
         <v>8</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8</v>
+        <v>0.795</v>
       </c>
       <c r="H22" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I22" t="n">
         <v>37.7</v>
       </c>
       <c r="J22" t="n">
-        <v>79</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.477</v>
+        <v>0.479</v>
       </c>
       <c r="L22" t="n">
         <v>7.6</v>
@@ -4331,37 +4398,37 @@
         <v>19.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0.389</v>
+        <v>0.392</v>
       </c>
       <c r="O22" t="n">
-        <v>22.7</v>
+        <v>22.4</v>
       </c>
       <c r="P22" t="n">
-        <v>27.1</v>
+        <v>26.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.838</v>
+        <v>0.836</v>
       </c>
       <c r="R22" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="S22" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="T22" t="n">
-        <v>43.4</v>
+        <v>43.1</v>
       </c>
       <c r="U22" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="V22" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="W22" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="Y22" t="n">
         <v>4.1</v>
@@ -4370,16 +4437,16 @@
         <v>20.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AB22" t="n">
-        <v>105.7</v>
+        <v>105.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4391,7 +4458,7 @@
         <v>1</v>
       </c>
       <c r="AH22" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AI22" t="n">
         <v>8</v>
@@ -4400,10 +4467,10 @@
         <v>29</v>
       </c>
       <c r="AK22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM22" t="n">
         <v>15</v>
@@ -4421,7 +4488,7 @@
         <v>1</v>
       </c>
       <c r="AR22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS22" t="n">
         <v>5</v>
@@ -4430,13 +4497,13 @@
         <v>10</v>
       </c>
       <c r="AU22" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AV22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX22" t="n">
         <v>2</v>
@@ -4448,7 +4515,7 @@
         <v>20</v>
       </c>
       <c r="BA22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E23" t="n">
         <v>14</v>
       </c>
       <c r="F23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G23" t="n">
-        <v>0.359</v>
+        <v>0.368</v>
       </c>
       <c r="H23" t="n">
         <v>48.4</v>
@@ -4501,16 +4568,16 @@
         <v>37.8</v>
       </c>
       <c r="J23" t="n">
-        <v>82.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="K23" t="n">
         <v>0.456</v>
       </c>
       <c r="L23" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M23" t="n">
-        <v>19.1</v>
+        <v>18.8</v>
       </c>
       <c r="N23" t="n">
         <v>0.353</v>
@@ -4519,22 +4586,22 @@
         <v>12.7</v>
       </c>
       <c r="P23" t="n">
-        <v>16.2</v>
+        <v>16.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.784</v>
+        <v>0.786</v>
       </c>
       <c r="R23" t="n">
         <v>10.3</v>
       </c>
       <c r="S23" t="n">
-        <v>32.2</v>
+        <v>32.4</v>
       </c>
       <c r="T23" t="n">
-        <v>42.5</v>
+        <v>42.7</v>
       </c>
       <c r="U23" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="V23" t="n">
         <v>14.7</v>
@@ -4549,19 +4616,19 @@
         <v>4.8</v>
       </c>
       <c r="Z23" t="n">
-        <v>19.7</v>
+        <v>19.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>95.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="AC23" t="n">
         <v>-3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AE23" t="n">
         <v>23</v>
@@ -4573,7 +4640,7 @@
         <v>23</v>
       </c>
       <c r="AH23" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AI23" t="n">
         <v>7</v>
@@ -4582,13 +4649,13 @@
         <v>13</v>
       </c>
       <c r="AK23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AN23" t="n">
         <v>17</v>
@@ -4609,10 +4676,10 @@
         <v>9</v>
       </c>
       <c r="AT23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV23" t="n">
         <v>14</v>
@@ -4627,13 +4694,13 @@
         <v>12</v>
       </c>
       <c r="AZ23" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
       </c>
       <c r="BB23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC23" t="n">
         <v>23</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -4665,43 +4732,43 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F24" t="n">
         <v>23</v>
       </c>
       <c r="G24" t="n">
-        <v>0.425</v>
+        <v>0.41</v>
       </c>
       <c r="H24" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>37.1</v>
+        <v>36.8</v>
       </c>
       <c r="J24" t="n">
-        <v>83.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.442</v>
+        <v>0.44</v>
       </c>
       <c r="L24" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="M24" t="n">
         <v>18.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0.357</v>
+        <v>0.361</v>
       </c>
       <c r="O24" t="n">
         <v>12.6</v>
       </c>
       <c r="P24" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="Q24" t="n">
         <v>0.722</v>
@@ -4713,10 +4780,10 @@
         <v>30.3</v>
       </c>
       <c r="T24" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U24" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="V24" t="n">
         <v>12.8</v>
@@ -4734,46 +4801,46 @@
         <v>18.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="AB24" t="n">
-        <v>93.2</v>
+        <v>92.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>-4.1</v>
+        <v>-4.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AF24" t="n">
         <v>20</v>
       </c>
       <c r="AG24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH24" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ24" t="n">
         <v>6</v>
       </c>
       <c r="AK24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL24" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AM24" t="n">
         <v>22</v>
       </c>
       <c r="AN24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4788,25 +4855,25 @@
         <v>22</v>
       </c>
       <c r="AS24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT24" t="n">
         <v>23</v>
       </c>
       <c r="AU24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AY24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ24" t="n">
         <v>5</v>
@@ -4818,7 +4885,7 @@
         <v>27</v>
       </c>
       <c r="BC24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>-4.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
         <v>26</v>
@@ -4946,7 +5013,7 @@
         <v>4</v>
       </c>
       <c r="AK25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL25" t="n">
         <v>25</v>
@@ -4955,7 +5022,7 @@
         <v>23</v>
       </c>
       <c r="AN25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO25" t="n">
         <v>26</v>
@@ -4970,16 +5037,16 @@
         <v>15</v>
       </c>
       <c r="AS25" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AT25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW25" t="n">
         <v>15</v>
@@ -5000,7 +5067,7 @@
         <v>18</v>
       </c>
       <c r="BC25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -5107,19 +5174,19 @@
         <v>-2.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
         <v>15</v>
       </c>
       <c r="AF26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AH26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI26" t="n">
         <v>19</v>
@@ -5137,19 +5204,19 @@
         <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP26" t="n">
         <v>21</v>
       </c>
       <c r="AQ26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR26" t="n">
         <v>12</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>13</v>
       </c>
       <c r="AS26" t="n">
         <v>21</v>
@@ -5167,7 +5234,7 @@
         <v>18</v>
       </c>
       <c r="AX26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY26" t="n">
         <v>4</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -5211,58 +5278,58 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E27" t="n">
         <v>15</v>
       </c>
       <c r="F27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G27" t="n">
-        <v>0.375</v>
+        <v>0.385</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>36.6</v>
+        <v>36.8</v>
       </c>
       <c r="J27" t="n">
-        <v>83.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="K27" t="n">
-        <v>0.439</v>
+        <v>0.442</v>
       </c>
       <c r="L27" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M27" t="n">
-        <v>18.8</v>
+        <v>19.1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.356</v>
+        <v>0.358</v>
       </c>
       <c r="O27" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="P27" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.767</v>
+        <v>0.769</v>
       </c>
       <c r="R27" t="n">
-        <v>12.1</v>
+        <v>12</v>
       </c>
       <c r="S27" t="n">
         <v>28.6</v>
       </c>
       <c r="T27" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="U27" t="n">
-        <v>19.8</v>
+        <v>20.1</v>
       </c>
       <c r="V27" t="n">
         <v>14.6</v>
@@ -5271,25 +5338,25 @@
         <v>8</v>
       </c>
       <c r="X27" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>96.90000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>-6</v>
+        <v>-5.7</v>
       </c>
       <c r="AD27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE27" t="n">
         <v>22</v>
@@ -5301,34 +5368,34 @@
         <v>22</v>
       </c>
       <c r="AH27" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM27" t="n">
         <v>17</v>
       </c>
-      <c r="AJ27" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>17</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>19</v>
-      </c>
       <c r="AN27" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO27" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AP27" t="n">
         <v>14</v>
       </c>
       <c r="AQ27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR27" t="n">
         <v>12</v>
@@ -5337,10 +5404,10 @@
         <v>29</v>
       </c>
       <c r="AT27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV27" t="n">
         <v>12</v>
@@ -5349,19 +5416,19 @@
         <v>14</v>
       </c>
       <c r="AX27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY27" t="n">
         <v>27</v>
       </c>
       <c r="AZ27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA27" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BB27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC27" t="n">
         <v>28</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -5393,79 +5460,79 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E28" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F28" t="n">
         <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>0.738</v>
+        <v>0.732</v>
       </c>
       <c r="H28" t="n">
         <v>48.6</v>
       </c>
       <c r="I28" t="n">
-        <v>39.7</v>
+        <v>39.8</v>
       </c>
       <c r="J28" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K28" t="n">
-        <v>0.486</v>
+        <v>0.487</v>
       </c>
       <c r="L28" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="N28" t="n">
-        <v>0.388</v>
+        <v>0.391</v>
       </c>
       <c r="O28" t="n">
         <v>16.4</v>
       </c>
       <c r="P28" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.795</v>
+        <v>0.792</v>
       </c>
       <c r="R28" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>33.3</v>
+        <v>33.1</v>
       </c>
       <c r="T28" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="U28" t="n">
-        <v>25.3</v>
+        <v>25.5</v>
       </c>
       <c r="V28" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W28" t="n">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X28" t="n">
         <v>5.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>104.5</v>
+        <v>104.8</v>
       </c>
       <c r="AC28" t="n">
         <v>8.4</v>
@@ -5474,7 +5541,7 @@
         <v>1</v>
       </c>
       <c r="AE28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF28" t="n">
         <v>3</v>
@@ -5516,16 +5583,16 @@
         <v>29</v>
       </c>
       <c r="AS28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW28" t="n">
         <v>5</v>
@@ -5537,7 +5604,7 @@
         <v>13</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA28" t="n">
         <v>26</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -5575,43 +5642,43 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E29" t="n">
         <v>14</v>
       </c>
       <c r="F29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G29" t="n">
-        <v>0.35</v>
+        <v>0.359</v>
       </c>
       <c r="H29" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="I29" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J29" t="n">
-        <v>82.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L29" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="M29" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="N29" t="n">
-        <v>0.348</v>
+        <v>0.345</v>
       </c>
       <c r="O29" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="P29" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="Q29" t="n">
         <v>0.775</v>
@@ -5620,16 +5687,16 @@
         <v>10.9</v>
       </c>
       <c r="S29" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="T29" t="n">
         <v>40.1</v>
       </c>
       <c r="U29" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="V29" t="n">
-        <v>12.9</v>
+        <v>12.7</v>
       </c>
       <c r="W29" t="n">
         <v>7.3</v>
@@ -5641,31 +5708,31 @@
         <v>5.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AA29" t="n">
         <v>19.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.09999999999999</v>
+        <v>97</v>
       </c>
       <c r="AC29" t="n">
-        <v>-2.1</v>
+        <v>-1.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE29" t="n">
         <v>23</v>
       </c>
       <c r="AF29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI29" t="n">
         <v>20</v>
@@ -5677,19 +5744,19 @@
         <v>22</v>
       </c>
       <c r="AL29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM29" t="n">
         <v>7</v>
       </c>
       <c r="AN29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP29" t="n">
         <v>12</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>13</v>
       </c>
       <c r="AQ29" t="n">
         <v>10</v>
@@ -5704,10 +5771,10 @@
         <v>28</v>
       </c>
       <c r="AU29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW29" t="n">
         <v>24</v>
@@ -5725,7 +5792,7 @@
         <v>15</v>
       </c>
       <c r="BB29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC29" t="n">
         <v>20</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -5835,16 +5902,16 @@
         <v>-0.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
         <v>13</v>
       </c>
       <c r="AF30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH30" t="n">
         <v>18</v>
@@ -5859,7 +5926,7 @@
         <v>13</v>
       </c>
       <c r="AL30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM30" t="n">
         <v>25</v>
@@ -5871,10 +5938,10 @@
         <v>5</v>
       </c>
       <c r="AP30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR30" t="n">
         <v>8</v>
@@ -5904,7 +5971,7 @@
         <v>28</v>
       </c>
       <c r="BA30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB30" t="n">
         <v>11</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
@@ -5939,67 +6006,67 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F31" t="n">
         <v>29</v>
       </c>
       <c r="G31" t="n">
-        <v>0.216</v>
+        <v>0.194</v>
       </c>
       <c r="H31" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="I31" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="J31" t="n">
-        <v>83.2</v>
+        <v>83.3</v>
       </c>
       <c r="K31" t="n">
-        <v>0.417</v>
+        <v>0.415</v>
       </c>
       <c r="L31" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M31" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0.334</v>
+        <v>0.33</v>
       </c>
       <c r="O31" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="P31" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.743</v>
+        <v>0.745</v>
       </c>
       <c r="R31" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S31" t="n">
         <v>32.4</v>
       </c>
       <c r="T31" t="n">
-        <v>43.8</v>
+        <v>43.7</v>
       </c>
       <c r="U31" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="V31" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="W31" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X31" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y31" t="n">
         <v>4.9</v>
@@ -6008,13 +6075,13 @@
         <v>20.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AB31" t="n">
-        <v>90.90000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="AC31" t="n">
-        <v>-6</v>
+        <v>-6.3</v>
       </c>
       <c r="AD31" t="n">
         <v>29</v>
@@ -6029,25 +6096,25 @@
         <v>30</v>
       </c>
       <c r="AH31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI31" t="n">
         <v>29</v>
       </c>
       <c r="AJ31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AK31" t="n">
         <v>30</v>
       </c>
       <c r="AL31" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AM31" t="n">
         <v>14</v>
       </c>
       <c r="AN31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO31" t="n">
         <v>25</v>
@@ -6056,13 +6123,13 @@
         <v>25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AR31" t="n">
         <v>17</v>
       </c>
       <c r="AS31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT31" t="n">
         <v>6</v>
@@ -6071,7 +6138,7 @@
         <v>20</v>
       </c>
       <c r="AV31" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AW31" t="n">
         <v>19</v>
@@ -6086,7 +6153,7 @@
         <v>22</v>
       </c>
       <c r="BA31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB31" t="n">
         <v>30</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-18-2012-13</t>
+          <t>2013-01-18</t>
         </is>
       </c>
     </row>
